--- a/results/问题四_改进求解/结果提交_问题四_改进求解.xlsx
+++ b/results/问题四_改进求解/结果提交_问题四_改进求解.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_分区与配置" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_资源汇总" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_中继复制明细" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径与来源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Q4_分区与配置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Q4_资源汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Q4_中继复制明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="口径与来源" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -534,12 +534,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S001、S002、S003、S004、S005、S006、S007、S008、S010、S011、S013、S014、S015</t>
+          <t>S001、S002、S003、S004、S005、S006、S007、S008、S009、S010、S011、S013、S014、S015</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>T01,T02,T03,T04,T06,T07,T08,T09,T10,T11,T12,T13,T14,T15,T16,T18,T19,T20,T21,T22</t>
+          <t>T01,T02,T03,T04,T06,T07,T08,T09,T10,T11,T12,T13,T14,T15,T16,T17,T18,T19,T20,T21,T22</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -561,13 +561,13 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>40985.782337</v>
+        <v>42544.22407</v>
       </c>
     </row>
     <row r="3">
@@ -586,12 +586,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S009、S012</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>T05,T17</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -613,13 +613,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3481.182084</v>
+        <v>1922.740351</v>
       </c>
     </row>
     <row r="4">
@@ -638,12 +638,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>S001、S002、S003、S004、S005、S006、S007、S008、S010、S011、S013、S014、S015</t>
+          <t>S001、S002、S003、S004、S005、S006、S007、S008、S009、S010、S011、S013、S014、S015</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>T01,T02,T03,T04,T06,T07,T08,T09,T10,T11,T12,T13,T14,T15,T16,T18,T19,T20,T21,T22</t>
+          <t>T01,T02,T03,T04,T06,T07,T08,T09,T10,T11,T12,T13,T14,T15,T16,T17,T18,T19,T20,T21,T22</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -665,13 +665,13 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>40985.782337</v>
+        <v>42544.22407</v>
       </c>
     </row>
     <row r="5">
@@ -690,12 +690,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S009、S012</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>T05,T17</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -717,13 +717,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>3481.182084</v>
+        <v>1922.740351</v>
       </c>
     </row>
     <row r="6">
@@ -742,40 +742,40 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S001、S002、S005、S008、S009、S010、S013、S014</t>
+          <t>S001、S002、S003、S004、S005、S006、S007、S008、S010、S011、S014、S015</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>T01,T02,T03,T06,T08,T09,T10,T11,T12,T14,T16,T17,T21</t>
+          <t>T01,T02,T03,T04,T06,T07,T08,T09,T11,T12,T13,T14,T15,T16,T18,T19,T20,T21,T22</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>24063.233055</v>
+        <v>39475.310012</v>
       </c>
     </row>
     <row r="7">
@@ -794,40 +794,40 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S003、S004、S006、S007、S011、S012、S015</t>
+          <t>S009、S012、S013</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>T04,T05,T07,T13,T15,T18,T19,T20,T22</t>
+          <t>T05,T10,T17</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>20403.731366</v>
+        <v>4991.654409</v>
       </c>
     </row>
     <row r="8">
@@ -846,12 +846,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S001、S002、S003、S004、S005、S006、S007、S008、S010、S011、S014、S015</t>
+          <t>S001、S002、S003、S004、S005、S006、S007、S008、S009、S010、S011、S014、S015</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>T01,T02,T03,T04,T06,T07,T08,T09,T11,T12,T13,T14,T15,T16,T18,T19,T20,T21,T22</t>
+          <t>T01,T02,T03,T04,T06,T07,T08,T09,T11,T12,T13,T14,T15,T16,T17,T18,T19,T20,T21,T22</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -873,13 +873,13 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>39475.310012</v>
+        <v>41033.751745</v>
       </c>
     </row>
     <row r="9">
@@ -898,12 +898,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S009、S013</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>T10,T17</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -925,13 +925,13 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>3068.914058</v>
+        <v>1922.740351</v>
       </c>
     </row>
     <row r="10">
@@ -950,12 +950,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -977,13 +977,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>1922.740351</v>
+        <v>1510.472325</v>
       </c>
     </row>
     <row r="11">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S001、S002、S003、S004、S005、S006、S007、S008、S010、S011、S014、S015</t>
+          <t>S001、S002、S003、S004、S005、S006、S007、S008、S009、S010、S011、S014、S015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>T01,T02,T03,T04,T06,T07,T08,T09,T11,T12,T13,T14,T15,T16,T18,T19,T20,T21,T22</t>
+          <t>T01,T02,T03,T04,T06,T07,T08,T09,T11,T12,T13,T14,T15,T16,T17,T18,T19,T20,T21,T22</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1029,13 +1029,13 @@
         <v>4</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>39475.310012</v>
+        <v>41033.751745</v>
       </c>
     </row>
     <row r="12">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>S009、S013</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>T10,T17</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1081,13 +1081,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>3068.914058</v>
+        <v>1922.740351</v>
       </c>
     </row>
     <row r="13">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1133,13 +1133,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1922.740351</v>
+        <v>1510.472325</v>
       </c>
     </row>
     <row r="14">
@@ -1158,40 +1158,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>S001、S002、S005、S008、S010、S014</t>
+          <t>S001、S002、S003、S004、S005、S006、S007、S008、S011、S014、S015</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>T01,T02,T03,T06,T08,T09,T11,T12,T14,T16,T21</t>
+          <t>T01,T02,T03,T04,T07,T08,T09,T11,T12,T13,T14,T15,T16,T18,T19,T20,T21,T22</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>20994.318997</v>
+        <v>37919.930446</v>
       </c>
     </row>
     <row r="15">
@@ -1210,40 +1210,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S003、S004、S006、S007、S011、S013、S015</t>
+          <t>S009、S012</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>T04,T07,T10,T13,T15,T18,T19,T20,T22</t>
+          <t>T05,T17</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>19991.46334</v>
+        <v>3481.182084</v>
       </c>
     </row>
     <row r="16">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>S009、S012</t>
+          <t>S010、S013</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>T05,T17</t>
+          <t>T06,T10</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1283,19 +1283,19 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>3481.182084</v>
+        <v>3065.851891</v>
       </c>
     </row>
   </sheetData>
@@ -1452,13 +1452,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E2" t="n">
-        <v>0.843426</v>
+        <v>0.913521</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
@@ -1479,10 +1479,10 @@
         <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1503,7 +1503,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1519,13 +1519,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>0.843426</v>
+        <v>0.913521</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -1546,10 +1546,10 @@
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1589,46 +1589,46 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
-        <v>0.082297</v>
+        <v>0.775489</v>
       </c>
       <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>1.176508</v>
+        <v>1.250482</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -1680,10 +1680,10 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>1.176508</v>
+        <v>1.250482</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
@@ -1747,10 +1747,10 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1787,40 +1787,40 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>36</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.101943</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="D7" t="n">
-        <v>29</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.54174</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
@@ -1829,16 +1829,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1855,7 +1855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1866,7 +1866,7 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="49" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RS04</t>
+          <t>RS02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1998,33 +1998,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>R-B4</t>
+          <t>R-B2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>西</t>
+          <t>东</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>T01,T02,T05,T06,T08,T10,T12,T16,T17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U0+U3+U4+U5+U6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>S003、S006、S007、S015</t>
+          <t>S001、S002、S005、S008、S009、S010、S013、S014</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RS01</t>
+          <t>RS03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2048,33 +2048,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>R-B1</t>
+          <t>R-B3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>西</t>
+          <t>北</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>T01,T03,T04,T07,T08,T09,T11,T12,T13,T14,T15,T16</t>
+          <t>T17,T18,T19,T20,T21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>U0+U1</t>
+          <t>U0+U2+U3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>S001、S002、S003、S005、S006、S007、S008、S014、S015</t>
+          <t>S001、S002、S004、S005、S008、S009、S011、S014</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2119,6 +2119,356 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>S003、S006、S007、S015</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>缺口优先</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RS02</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>R-B2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>东</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>T01,T02,T05,T06,T08,T10,T12,T16,T17</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>U0+U3+U4+U5+U6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>S012</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>缺口优先</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RS01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>R-B1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>西</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>T01,T03,T04,T07,T08,T09,T11,T12,T13,T14,T15,T16</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>U0+U1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>S001、S002、S003、S005、S006、S007、S008、S014、S015</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>缺口优先</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RS02</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>R-B2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>东</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>T01,T02,T05,T06,T08,T10,T12,T16,T17</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>U0+U3+U4+U5+U6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>S001、S002、S005、S008、S009、S010、S014</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>缺口优先</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RS03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>R-B3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>北</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>T17,T18,T19,T20,T21</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>U0+U2+U3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>S001、S002、S004、S005、S008、S009、S011、S014</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>缺口优先</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RS04</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>R-B4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>西</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>T22</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>S003、S006、S007、S015</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>缺口优先</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RS02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>R-B2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>东</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>T01,T02,T05,T06,T08,T10,T12,T16,T17</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>U0+U3+U4+U5+U6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>S012</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>缺口优先</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RS02</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>R-B2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>东</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>T01,T02,T05,T06,T08,T10,T12,T16,T17</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>U0+U3+U4+U5+U6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>S013</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2510,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D:\git\math_modeling\UAV\code\问题三_改进求解\plan_windows_opt.json</t>
+          <t>C:\Users\71523\Documents\Codex\2026-09-25\https-github-com-a1585425912-uav-https\work\UAV\code\问题三_改进求解\plan_windows_opt.json</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2522,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0bbdca1a962edaf6b736bb5be10dc7de3ecb79f567e3594d6891c900156fa314</t>
+          <t>77aa79573689cd6afde66a3a83450fa33f56040e8316553bf0f000f5565fab77</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2533,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8914.079576916525</v>
+        <v>8915.079576916525</v>
       </c>
     </row>
     <row r="5">
@@ -2298,7 +2648,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中继架次保障的全部单元都落在同一任务组时，该组独立配置一整架次；跨组则每组各配一套</t>
+          <t>中继架次只要保障到本组任一单元，该组就独立配置一整架次；跨组时各相关组各配一套</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2708,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>results/问题三_参考口径/主方案_完整方案.json（9573.284 s）；code/问题三_改进求解/plan_3relay_fixed_final.json（未获 100% 连续认证）</t>
+          <t>results/问题三_参考口径/主方案_完整方案.json（9573.284 s，已在清理中移除，可由 python code/问题三四_复现.py 重建）；code/问题三_改进求解/plan_3relay_fixed_final.json（未获 100% 连续认证）</t>
         </is>
       </c>
     </row>
